--- a/output/pdf_financials_xlsx/STGX.xlsx
+++ b/output/pdf_financials_xlsx/STGX.xlsx
@@ -1922,13 +1922,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0.477716</v>
+        <v>0.598896</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0.477716</v>
+        <v>0.478377</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.924754</v>
       </c>
     </row>
     <row r="93">
@@ -2329,13 +2329,13 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>1.78187</v>
+        <v>1.478468</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0.06435</v>
+        <v>-3.276926</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-1.122864</v>
       </c>
     </row>
     <row r="119">
@@ -3472,7 +3472,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>
@@ -5005,7 +5009,11 @@
           <t>Warrant reserve</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E76" s="5" t="n">
         <v>0.12118</v>
       </c>
@@ -5776,7 +5784,11 @@
           <t>Deferred exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
           <t>-</t>
@@ -6842,7 +6854,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E135" s="5" t="n">
         <v>-0.303402</v>
       </c>

--- a/output/pdf_financials_xlsx/STGX.xlsx
+++ b/output/pdf_financials_xlsx/STGX.xlsx
@@ -982,13 +982,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.005766</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.108756</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.265585</v>
       </c>
     </row>
     <row r="35">
@@ -1014,13 +1014,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.005766</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.108756</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.265585</v>
       </c>
     </row>
     <row r="37">
@@ -1206,13 +1206,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.019728</v>
+        <v>0.013962</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.042904</v>
+        <v>0.934148</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.275969</v>
+        <v>0.010384</v>
       </c>
     </row>
     <row r="49">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -4121,7 +4121,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E48" s="5" t="n">

--- a/output/pdf_financials_xlsx/STGX.xlsx
+++ b/output/pdf_financials_xlsx/STGX.xlsx
@@ -6548,7 +6548,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E125" s="5" t="n">
         <v>0.17</v>
       </c>
